--- a/watchlist.xlsx
+++ b/watchlist.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not Watchable" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Watching'!$A$1:$F$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Watching'!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog'!$A$1:$D$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Not Watchable'!$A$1:$B$22</definedName>
   </definedNames>
@@ -23,17 +23,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <color rgb="000563C1"/>
-      <u val="single"/>
     </font>
     <font>
       <b val="1"/>
@@ -64,10 +60,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -476,764 +471,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ada</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/ada18</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>39</v>
-      </c>
-      <c r="E3" t="n">
-        <v>388</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Applied Intuition</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>248</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/applied</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Augment</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/augmentcomputing</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Clay</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>17</v>
-      </c>
-      <c r="E6" t="n">
-        <v>81</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/claylabs</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cohere</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" t="n">
-        <v>127</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/cohere</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Cresta</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E8" t="n">
-        <v>104</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/cresta</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Decagon</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>9</v>
-      </c>
-      <c r="E9" t="n">
-        <v>114</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/decagon</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>24</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Fivetran</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>13</v>
-      </c>
-      <c r="E11" t="n">
-        <v>132</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/fivetran</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Glean</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>15</v>
-      </c>
-      <c r="E12" t="n">
-        <v>137</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gleanwork</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Gong</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>96</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gongio</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Harvey</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>27</v>
-      </c>
-      <c r="E14" t="n">
-        <v>329</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/harvey</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Hebbia</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>34</v>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/hebbia-ai</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Hightouch</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" t="n">
-        <v>63</v>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/hightouch</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Mistral</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>lever</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>175</v>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/mistral</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Nuro</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>6</v>
-      </c>
-      <c r="E18" t="n">
-        <v>94</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/nuro</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>53</v>
-      </c>
-      <c r="E19" t="n">
-        <v>724</v>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/openai</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Parloa</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" t="n">
-        <v>54</v>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/parloa</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Perplexity</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" t="n">
-        <v>78</v>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/perplexity</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Sana</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>31</v>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/sana-roles</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Sierra</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>15</v>
-      </c>
-      <c r="E23" t="n">
-        <v>147</v>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/sierra</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Sigma Computing</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>5</v>
-      </c>
-      <c r="E24" t="n">
-        <v>70</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/sigmacomputing</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Sourcegraph</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>6</v>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/sourcegraph91</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Writer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>49</v>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/writer</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>xAI</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>curated</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>214</v>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/xai</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F27"/>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId26"/>
-  </hyperlinks>
+  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/watchlist.xlsx
+++ b/watchlist.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not Watchable" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Watching'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog'!$A$1:$D$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Watching'!$A$1:$F$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog'!$A$1:$D$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Not Watchable'!$A$1:$B$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
     <font>
       <b val="1"/>
@@ -60,9 +64,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -471,8 +476,793 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ada</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/ada18</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>39</v>
+      </c>
+      <c r="E3" t="n">
+        <v>388</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Applied Intuition</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>248</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Augment</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/augmentcomputing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E6" t="n">
+        <v>81</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/claylabs</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cohere</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>127</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/cohere</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cresta</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>104</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/cresta</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Decagon</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>114</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/decagon</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dust</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>auto (new today)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>17</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/dust</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/figure</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13</v>
+      </c>
+      <c r="E12" t="n">
+        <v>132</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/fivetran</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Glean</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>15</v>
+      </c>
+      <c r="E13" t="n">
+        <v>137</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gleanwork</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gong</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>96</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gongio</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>27</v>
+      </c>
+      <c r="E15" t="n">
+        <v>329</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/harvey</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Hebbia</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>34</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/hebbia-ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Hightouch</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>63</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/hightouch</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Mistral</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>lever</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>177</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/mistral</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Nuro</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>94</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/nuro</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Observe.AI</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>auto (new today)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>14</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/observeai</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Parloa</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>54</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/parloa</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>78</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/perplexity</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sana</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>31</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sana-roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>15</v>
+      </c>
+      <c r="E24" t="n">
+        <v>147</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sierra</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sigma Computing</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>70</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/sigmacomputing</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sourcegraph</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/sourcegraph91</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Writer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>49</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/writer</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>214</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/xai</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F28"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -483,7 +1273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -517,73 +1307,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dust</t>
+          <t>Hex</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dust</t>
+          <t>hextechnologies</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>enterprise AI agents, like Glean/Sierra</t>
+          <t>data/analytics, like Hightouch</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Observe.AI</t>
+          <t>Distyl</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>observeai</t>
+          <t>distyl</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>contact-center AI, like Cresta</t>
+          <t>enterprise AI, like Writer</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hex</t>
+          <t>Omni</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>hextechnologies</t>
+          <t>omni</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>data/analytics, like Hightouch</t>
+          <t>BI/data, like Hightouch</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Distyl</t>
+          <t>Mercor</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -593,41 +1383,41 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>distyl</t>
+          <t>mercor</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>enterprise AI, like Writer</t>
+          <t>AI data/talent, like Scale AI</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Omni</t>
+          <t>PolyAI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>omni</t>
+          <t>polyai</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BI/data, like Hightouch</t>
+          <t>voice agents, like Sierra/Decagon</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mercor</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -637,19 +1427,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mercor</t>
+          <t>airbyte</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AI data/talent, like Scale AI</t>
+          <t>data integration, like Hightouch</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PolyAI</t>
+          <t>Vectara</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -659,19 +1449,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>polyai</t>
+          <t>vectara</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>voice agents, like Sierra/Decagon</t>
+          <t>enterprise search/RAG, like Glean</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Abridge</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -681,41 +1471,41 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>airbyte</t>
+          <t>abridge</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>data integration, like Hightouch</t>
+          <t>healthcare vertical AI, like Harvey</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Vectara</t>
+          <t>MotherDuck</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>vectara</t>
+          <t>motherduck</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>enterprise search/RAG, like Glean</t>
+          <t>data warehouse, like Hightouch</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Abridge</t>
+          <t>Credal</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -725,19 +1515,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>abridge</t>
+          <t>credal</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>healthcare vertical AI, like Harvey</t>
+          <t>enterprise AI, like Glean</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MotherDuck</t>
+          <t>Lorikeet</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -747,19 +1537,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>motherduck</t>
+          <t>lorikeet</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>data warehouse, like Hightouch</t>
+          <t>support agents, like Decagon</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Credal</t>
+          <t>Ambience</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -769,19 +1559,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>credal</t>
+          <t>ambiencehealthcare</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>enterprise AI, like Glean</t>
+          <t>healthcare vertical AI, like Harvey</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lorikeet</t>
+          <t>OpenEvidence</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -791,19 +1581,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>lorikeet</t>
+          <t>openevidence</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>support agents, like Decagon</t>
+          <t>medical knowledge AI, like Harvey</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ambience</t>
+          <t>Replit</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -813,19 +1603,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ambiencehealthcare</t>
+          <t>replit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>healthcare vertical AI, like Harvey</t>
+          <t>AI coding, like OpenAI</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OpenEvidence</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -835,19 +1625,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>openevidence</t>
+          <t>cursor</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>medical knowledge AI, like Harvey</t>
+          <t>AI coding, like Anthropic/OpenAI</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Replit</t>
+          <t>Cognition</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -857,19 +1647,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>replit</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AI coding, like OpenAI</t>
+          <t>coding agents, like OpenAI</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>ElevenLabs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -879,19 +1669,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>cursor</t>
+          <t>elevenlabs</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AI coding, like Anthropic/OpenAI</t>
+          <t>voice gen AI, like OpenAI</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cognition</t>
+          <t>Reka</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -901,19 +1691,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>reka</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>coding agents, like OpenAI</t>
+          <t>foundation lab, like Cohere/Mistral</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ElevenLabs</t>
+          <t>Liquid AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -923,19 +1713,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>elevenlabs</t>
+          <t>liquid</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>voice gen AI, like OpenAI</t>
+          <t>foundation lab, like Mistral</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Reka</t>
+          <t>Poolside</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -945,19 +1735,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>reka</t>
+          <t>poolside</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>foundation lab, like Cohere/Mistral</t>
+          <t>AI coding, like Anthropic</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Liquid AI</t>
+          <t>Suno</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -967,149 +1757,105 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>liquid</t>
+          <t>suno</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>foundation lab, like Mistral</t>
+          <t>generative audio, like Runway</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Poolside</t>
+          <t>World Labs</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>poolside</t>
+          <t>worldlabs</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AI coding, like Anthropic</t>
+          <t>spatial AI, like OpenAI</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Suno</t>
+          <t>Wayve</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>suno</t>
+          <t>wayve</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>generative audio, like Runway</t>
+          <t>autonomous driving, like Nuro</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>World Labs</t>
+          <t>Waabi</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>worldlabs</t>
+          <t>waabi</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>spatial AI, like OpenAI</t>
+          <t>autonomous driving, like Nuro</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Wayve</t>
+          <t>1X</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>wayve</t>
+          <t>1x</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>autonomous driving, like Nuro</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Waabi</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>lever</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>waabi</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>autonomous driving, like Nuro</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>1X</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1x</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
           <t>humanoid robotics, like Figure</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D28"/>
+  <autoFilter ref="A1:D26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
